--- a/docs/templates/m1-画像技术栈评估表.xlsx
+++ b/docs/templates/m1-画像技术栈评估表.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>I2C（必会）；CAN（必会）；SPI（必会）；CAPL（必会）；Test Module 自动化测试开发（必会）；UDS 14229/15765（必会）；CANoe（必会）；CANalyzer（必会）；INCA（必会）；C#（必会）；C++（必会）；Python（必会）；汽车控制器测试脚本开发经验（加分）；嵌入式测试经验（加分）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -498,7 +498,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>CANoe；CANalyzer；INCA；CAPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -518,7 +518,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>UDS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -558,7 +558,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -598,7 +598,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>I2C（必会）；CAN（必会）；SPI（必会）；嵌入式C底层软件开发（必会）；底层驱动开发（必会）；软件集成（必会）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>hightec；tasking</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>Freescale；英飞凌</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -658,7 +658,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>用友ERP操作（必会）；MRP功能（必会）；办公软件（Excel函数计算）（必会）；采购体系管理经验（必会）；采购保供订单管理（必会）；新产品/新工具/新物料询价（必会）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -818,7 +818,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>用友ERP（必会）；Excel函数计算（必会）；采购谈判策略与降本方法（必会）；采购保供订单管理（必会）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -858,7 +858,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -878,7 +878,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -918,7 +918,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>文案撰写（文章、新闻稿、软文）（必会）；宣传物料制作（海报、视频、PPT）（必会）；线上品牌推广（官网SEO、公众号、媒体传播）（必会）；展会与技术会议等线下市场活动策划执行（必会）；商用车/工程机械/柴油机行业市场认知（必会）</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>SPC（必会）；MSA（必会）；PMEA（必会）；APQP（必会）；PPAP（必会）；VDA6.3（必会）；VDA6.5（必会）；汽车质量管理体系（必会）；SMT工艺（必会）；压铸件工艺（必会）；冲压件工艺（必会）</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>功率器件应用（IGBT/SiC MOSFET模块选型、驱动保护、并联均流）（必会）；主功率回路与DC-Link、采样电路设计（必会）；高压辅助电源设计（DCDC、隔离电源、门极驱动电源）（必会）；电机控制器硬件架构与电流/电压/温度/旋变接口电路（必会）；汽车电子EMC设计规范（CISPR 25、ISO 11452）与EMC整改（必会）；功能安全（ISO 26262）硬件开发（必会）；800V高压平台电驱硬件开发（加分）；硬件安全机制（HARA、FMEDA）（加分）</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>CANoe/CANape 总线工具（必会）；SAE J1939 整车通信协议（必会）；Altium/Cadence PCB 设计软件（看懂原理图、评估硬件方案）（必会）；SRS/DFMEA/测试规范/产品规格等技术文档编制（必会）；ISO16750/ISO7637/ISO6469、商用车高压安全、EMC、功能安全基础规范（必会）</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>CANoe；CANape；Altium；Cadence</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>汽车电子电气架构（必会）；SoC设计流程及高性能计算芯片（必会）；功能安全 ISO 26262（必会）；ASPICE开发流程（必会）；系统需求分析与系统架构设计（必会）</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>⏸ 留步：未取得</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
